--- a/문서/의료진이 주도하는 ai 전환의 현장 이야기_dataset 구조.xlsx
+++ b/문서/의료진이 주도하는 ai 전환의 현장 이야기_dataset 구조.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emr4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\유현\개발\의료AX\문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{695A9A06-2922-48F6-9488-4E090B2133E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259D3FF5-1A3F-4E4B-924B-42DB138FE99E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{075A7942-26BC-4EFD-85B0-C0D52DAD1022}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,6 +156,10 @@
   </si>
   <si>
     <t>처방약물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -538,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F047CFA7-B16D-4895-8CE6-EC934FCBD02F}">
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
@@ -677,6 +681,11 @@
         <v>29</v>
       </c>
     </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="S8" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
